--- a/Data/Export/Common/JobType_指令.xlsx
+++ b/Data/Export/Common/JobType_指令.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29530"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr updateLinks="always" codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\sango_infinity\Data\Export\Common\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2D129C04-C606-4737-9F53-198B2C3441B3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{175AC5CD-5F06-42FE-8458-FFF5BD4053F9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="923" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="200" uniqueCount="80">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="216" uniqueCount="86">
   <si>
     <t>0</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -330,6 +330,30 @@
   </si>
   <si>
     <t>军事驻守</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>外交送礼</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>外交/送礼</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>30</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1000</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>外交同盟</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>外交/同盟</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1601,14 +1625,68 @@
       </c>
     </row>
     <row r="26" spans="2:11" x14ac:dyDescent="0.15">
-      <c r="B26" s="4"/>
-      <c r="C26" s="4"/>
-      <c r="J26" s="4"/>
-    </row>
-    <row r="27" spans="2:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.15">
-      <c r="B27" s="4"/>
-      <c r="C27" s="4"/>
-      <c r="J27" s="4"/>
+      <c r="B26" s="4">
+        <v>22</v>
+      </c>
+      <c r="C26" s="4" t="s">
+        <v>80</v>
+      </c>
+      <c r="D26" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="E26" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="F26" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="G26" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="H26" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="I26" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="J26" s="4">
+        <v>1</v>
+      </c>
+      <c r="K26" s="2" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="2:11" x14ac:dyDescent="0.15">
+      <c r="B27" s="4">
+        <v>23</v>
+      </c>
+      <c r="C27" s="4" t="s">
+        <v>84</v>
+      </c>
+      <c r="D27" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="E27" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="F27" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="G27" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="H27" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="I27" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="J27" s="4">
+        <v>1</v>
+      </c>
+      <c r="K27" s="2" t="s">
+        <v>0</v>
+      </c>
     </row>
     <row r="28" spans="2:11" x14ac:dyDescent="0.15">
       <c r="B28" s="4"/>
